--- a/exps_cmp.xlsx
+++ b/exps_cmp.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14380"/>
+    <workbookView windowWidth="29400" windowHeight="14380" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Pi-Long KITTI" sheetId="6" r:id="rId1"/>
